--- a/outputs/外注テスト手順書_2026-07-02.xlsx
+++ b/outputs/外注テスト手順書_2026-07-02.xlsx
@@ -7,7 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="手順書" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_このシステムについて" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_画面の構成" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_テストの準備" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_進め方と記入ルール" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38,7 +41,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +51,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DBEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF9C3"/>
       </patternFill>
     </fill>
   </fills>
@@ -63,13 +71,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,11 +446,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B35"/>
+  <dimension ref="B1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="108" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -462,204 +473,648 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>1. このテストの目的</t>
+          <t>1-1. どんなシステム？</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>英会話ゲーム「English Speaking Drill」が仕様どおりに動くこと、および直近の改修（音声・画面・ログインまわり）が直っていることを確認します。</t>
+          <t>英語教室の生徒（小学生〜中学生）が使う、英語の発話練習ゲームです。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>テストする内容はすべて「外注テスト項目書」に書いてあります。専門知識は不要です。書かれた手順どおりに操作して、結果を記入してください。</t>
+          <t>画面に英語の問題が出て、生徒は「マイクに向かって英語で答え」ます。正解すると敵キャラクターを攻撃でき、間違えると反撃される、シューティングゲーム仕立てになっています。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>問題は「中1・中2・中3」の3学年に分かれ、その中が「パート」と「サブパート」という単位に分かれています（例: 中3のパート8のサブパート2 → 3-8-2 と表記）。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>2. 準備するもの</t>
+      <c r="B8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>1-2. 遊び方の流れ（全体像）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>ログイン → ステージ選択 → ゲーム（8問） → 結果画面 → 次のステージへ…</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>この流れを繰り返して、生徒は少しずつ先のステージに進んでいきます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>1-3. ゲームの基本ルール（テスト前にこれだけは覚えてください）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>・1ステージは8問。ただし1問目は「お手本（デモ）」で、自動で正解が表示されます。生徒が実際に答えるのは残りの7問です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>・各問題の制限時間は30秒。時間内なら何度でも答え直せます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>・問題文の音声は毎回2回読み上げられ、そのあと回答できるようになります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>・7問中5問正解すると「クリア」となり、次のステージが選べるようになります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>・クリアできなくても、同じステージを10回プレイすると自動で次のステージに進めます（生徒が詰まって先に進めなくなるのを防ぐ仕組みです）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>・答えの判定はおおらかです。短縮形（I'm と I am など）はどちらでも正解になります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>1-4. 用語集</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>・Grade／Part／Subpart … 学年／パート／サブパート。ステージ選択画面で選びます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>・Requirement（回答条件） … ゲーム開始前に表示される「このステージの答え方のルール」（日本語）。画面に表示されるだけで、音声では読まれません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>・デモ問題 … 各ステージの1問目。自動で正解が表示されるお手本です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>・銃のボタン … 画面下の大きなボタン。押すとマイクON、もう一度押すと回答確定です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>・Heard … 画面右上に出る「マイクが聞き取った言葉」です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>・フリーズ回復画面 … 万一ゲームが固まったとき、20秒ほどで自動表示される画面。「リトライ／次の問題へ／やめる」を選べます。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:B22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="108" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>画面の構成（全部で6画面あります）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>① ログイン画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>最初に表示される画面。「Welcome to English Game!」というタイトルと、User ID・Passwordの入力欄、「LOGIN」ボタンがあります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>できること: ログイン。生徒はステージ選択画面へ、先生（管理者）は管理者画面へ移動します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>② ステージ選択画面（Select a Stage）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Grade（学年）・Part（パート）・Subpart（サブパート）の3つのプルダウンと「Game Start」ボタン、右上に「Ranking 🏆」ボタンがあります。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>・パソコン（Google Chrome 最新版）※音声認識のテストはChromeで行ってください</t>
+          <t>できること: 遊ぶステージを選んでゲーム開始。自分の進み具合より先のステージはプルダウンに表示されず、選べません。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>・マイク（内蔵マイクでOK）とスピーカー（またはイヤホン）</t>
+      <c r="B10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>③ ゲーム画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>メインの画面です。上に敵キャラクター、中央に問題文（イラストつきの問題は右側にイラスト）、左に「いま何問目か」の数字と残り時間のタイマー、下に銃のボタン（マイク）、左上に「やめる」ボタンがあります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>できること: 音声を聞いて、マイクで英語で回答。正解すると敵を攻撃する演出、不正解だと敵に攻撃される演出が出ます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>④ 結果画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>ステージ終了後に表示。スコア（正解数/7とパーセント）、クリアの可否（CLEAR／FAILED）、「あと N 問正解でクリア！」などのメッセージ、「LOGOUT」と「NEXT（またはRetry）」ボタンがあります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>⑤ ランキング画面（Ranking 👑）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>今月の「Number of try」（挑戦回数）と「Best Scores」（成績）の上位3名のニックネームが表示されます。月が替わるとリセットされます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>⑥ 管理者画面（先生用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>管理者でログインしたときだけ表示。生徒の新規登録（ID・パスワードの発行）、生徒の進捗（学年・パート）の確認と変更、パスワードリセット、パートごとのミス数の一覧が使えます。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:B22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="108" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>テストの準備</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>3-1. 必要なもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>・パソコン（WindowsでもMacでも可）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>・Google Chrome（最新版）※他のブラウザは使わないでください</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>・マイク（パソコン内蔵のものでOK）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>・スピーカーまたはイヤホン（音声を聞く項目があります）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>・スマホやタブレットは不要です（このテストはパソコンのChromeだけで行います）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>3-2. テスト用URLとアカウント（藤岡から別途お渡しします）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>・できればiPadまたはiPhone（横画面の確認用。なければパソコンのみでOK）</t>
+          <t>テスト用URL: ＿＿＿＿＿＿＿＿＿＿＿＿＿＿＿＿＿＿＿＿</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>・テスト用URL・テスト用のユーザーIDとパスワード（別途お渡しします）</t>
+          <t>ユーザーA（全ステージ選択可能な生徒）: ID ＿＿＿＿＿ ／ パスワード ＿＿＿＿＿</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>ユーザーB（進捗が途中の生徒。ステージ制限などの確認用）: ID ＿＿＿＿＿ ／ パスワード ＿＿＿＿＿</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>3. はじめる前の設定</t>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　→ ユーザーBの現在の進捗: 学年＿＿・パート＿＿・サブパート＿＿</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>① Chromeでテスト用URLを開く</t>
+          <t>管理者（先生役）: ID ＿＿＿＿＿ ／ パスワード ＿＿＿＿＿</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>※テスト項目書に「ユーザーA」「ユーザーB」「管理者」と書かれていたら、上の対応するアカウントを使ってください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>3-3. はじめる前の設定（1回だけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>① ChromeでテストURLを開く。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>② 初めてマイクを使う場面で、アドレスバーの下に「マイクの使用を許可しますか？」という確認が出たら「許可する」を押す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>③ パソコンの音量を中くらいにして、音が出ることを確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>※誤って「ブロック」を押してしまった場合: アドレスバー左端の鍵（または設定）アイコン → 「マイク」を「許可」に変更 → ページを再読み込みしてください。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="108" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>テストの進め方と記入ルール</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>4-1. 実施する順番（おすすめ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>① まず「外注テスト項目書」のシート「B_要望確認テスト」の No.136（ログインに時間がかかる件）を、テスト初日の一番最初に実施する（誰も使っていない状態が必要なため）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>② シート「A_機能テスト」を上から順に実施する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>③ シート「B_要望確認テスト」の残りを上から順に実施する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>④ 「時間条件つき」と書かれた項目（24時間放置が必要なもの）は、初日にログインだけして画面を開いたままにしておき、翌日に実施する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>⑤ 「発生した場合のみ」と書かれた項目は、その現象が起きたときだけ記入する（起きなければ結果欄に「発生せず」と書く）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>4-2. 各項目のやり方</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>・「事前準備」の状態を作ってから、「操作手順」の①②③…を順番どおりに行ってください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>・「期待する結果」のとおりになったら「結果」欄に OK、ならなかったら NG と記入してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>・見逃してしまった場合は、同じ手順を最初からやり直してかまいません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>4-3. NGだったときの書き方（重要）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>② 最初にマイクの許可を求められたら「許可」を押す</t>
+          <t>備考欄に次の3点を書いてください:</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>③ 音が出ることを確認する（音量は中くらいに）</t>
+          <t>（1）どの手順番号まで進んだか（例: ③まで実施）</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>（2）実際にどうなったか（例: 音声が1回しか流れなかった）</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>4. テストの進め方</t>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>（3）スクリーンショットの有無（撮れたら画像ファイルを一緒に送ってください）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>① 「外注テスト項目書」を開き、上から順に1件ずつ実施します</t>
+          <t>・スクリーンショットの撮り方: Windowsは「Windowsキー＋Shift＋S」、Macは「command＋shift＋4」で範囲を選んで撮れます。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>② 各行の「手順」どおりに操作し、「期待結果」のとおりになるか確認します</t>
+          <t>・画面に英数字のコード（例: AUTH-001、TTS-001）が表示された場合は、そのコードも備考に書いてください（原因の特定がとても早くなります）。</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>③ 「結果」列に OK または NG を記入します</t>
-        </is>
-      </c>
+      <c r="B22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>④ NGの場合は「備考」列に、（1）何をしたか（2）何が起きたか（3）画面のスクリーンショットの有無を書いてください。スクリーンショットはファイルで添付してもらえると助かります</t>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>4-4. 困ったとき</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>⑤ 表示が一瞬で見逃した場合などは、同じ手順をもう一度やり直してかまいません</t>
+          <t>・画面が完全に動かなくなった → 20秒ほど待つと復帰画面が出ます。出ない場合はキーボードのF5（Macはcommand＋R）で再読み込みし、状況を備考に書いてください。</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>・ログインできない／URLが開けない → 藤岡までご連絡ください。</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>5. 注意事項</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>・シート「A_機能テスト」は仕様からランダムに選んだ確認項目です</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>・シート「B_要望確認テスト」は、これまでに報告のあった不具合・要望が直っているかの確認です。全件実施してください</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>・「（発生した場合のみ）」と書かれた項目は、その現象が起きたときだけ記入してください</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>・音声の聞こえ方（発音など）は主観でかまいません。気になったことは何でも備考に書いてください</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>・途中でゲームが完全に動かなくなった場合は、ページを再読み込み（F5）して続けてください。その際は必ず備考に状況を書いてください</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>6. 困ったとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>・ログインできない／URLが開けない → 藤岡までご連絡ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>・エラーメッセージに英数字のコード（例: AUTH-001）が出た場合は、そのコードを備考に書いてください</t>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>・音声の聞こえ方（発音など）の判断は主観でかまいません。迷ったら「気になった」と備考に書いてください。</t>
         </is>
       </c>
     </row>

--- a/outputs/外注テスト手順書_2026-07-02.xlsx
+++ b/outputs/外注テスト手順書_2026-07-02.xlsx
@@ -785,7 +785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B22"/>
+  <dimension ref="B1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -897,38 +897,45 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="2" t="inlineStr"/>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>※管理画面のテストでは、テスターA・テスターB以外のユーザー（実際の生徒・先生のアカウント）には絶対に触れないでください。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>3-3. はじめる前の設定（1回だけ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>① ChromeでテストURLを開く。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>② 初めてマイクを使う場面で、アドレスバーの下に「マイクの使用を許可しますか？」という確認が出たら「許可する」を押す。</t>
+          <t>① ChromeでテストURLを開く。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="2" t="inlineStr">
         <is>
+          <t>② 初めてマイクを使う場面で、アドレスバーの下に「マイクの使用を許可しますか？」という確認が出たら「許可する」を押す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>③ パソコンの音量を中くらいにして、音が出ることを確認する。</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="4" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>※誤って「ブロック」を押してしまった場合: アドレスバー左端の鍵（または設定）アイコン → 「マイク」を「許可」に変更 → ページを再読み込みしてください。</t>
         </is>

--- a/outputs/外注テスト手順書_2026-07-02.xlsx
+++ b/outputs/外注テスト手順書_2026-07-02.xlsx
@@ -563,7 +563,7 @@
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>・クリアできなくても、同じステージを10回プレイすると自動で次のステージに進めます（生徒が詰まって先に進めなくなるのを防ぐ仕組みです）。</t>
+          <t>・クリアできなくても、同じステージを3回プレイすると自動で次のステージに進めます（生徒が詰まって先に進めなくなるのを防ぐ仕組みです）。</t>
         </is>
       </c>
     </row>
